--- a/affiliate_data/เครื่องใช้ในบ้าน.xlsx
+++ b/affiliate_data/เครื่องใช้ในบ้าน.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ แบบพกพา พร้อมปั๊มลมในตัว ที่นอนลม แบบหนา 40/25ซม</v>
+        <v>TYESO รุ่นใหม่ 2026 แก้วเก็บความเย็นลายดอกไม้ 900ML แก้วเก็บอุณหภูมิสแตนเลส พร้อมหลอด เก็บเย็น 24H ร้อน 12H</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m66kvsnez2tt31.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>829.00</v>
+        <v>309.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 455 ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/25326987298</v>
+        <v>https://shopee.co.th/product/0/54857018813</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/1Ld1LV2o10</v>
+        <v>https://s.shopee.co.th/9Uyt87gFze</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>10</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3">
@@ -480,31 +480,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>5เเพ็ค กระดาษทิชชู่ Sipeau กระดาษทิชชู่คุณภาพสูง นุ่ม กระดาษทิชชู่เช็ดหน้า</v>
+        <v>Ozama บัลลังก์ รุ่น Alpha เก้าอี้เกมมิ่ง Gaming Chair by Tengu รับน้ำหนัก 150กก Throne of Gamer</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mozcimjqsxs236.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>109.00</v>
+        <v>6990.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 425 ชิ้น</v>
+        <v>ขายได้ 2พัน+ ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/53009007936</v>
+        <v>https://shopee.co.th/product/0/24014645473</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/5VSaJ9u5pe</v>
+        <v>https://s.shopee.co.th/110L0VMRke</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -518,37 +518,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>ลวดหนาม (ชุบกัลวาไนซ์) ยาว120-200m (เบอร์14 16 17) ล้อมรั้วราคาถูก ลวดหนามเหล็กติดรั้ว ล้อมรั้ว ลวดหนาม</v>
+        <v>หมอน ErgoLab Deep Sleep หมดปัญหาปวดคอ ไม่ต้องกังวลเรื่องกรน หลับสบายต่อเนื่องตลอดคืน (คืนเงินใน 90 วัน + รับประกัน 1 ปี)</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lop0pq60fv3x2c.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>710.00</v>
+        <v>1411.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 90พัน+ ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://shopee.co.th/product/0/5379453788</v>
+        <v>https://shopee.co.th/product/0/23922419352</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/2qRp8GDWdu</v>
+        <v>https://s.shopee.co.th/5fmAZ5DTpk</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -556,31 +556,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ถึง160°c สีครีม เบาะฟองน้ำหนา10ซม. นุ่มสบาย ผ้ากำมะหยี่</v>
+        <v>Maybuck เครื่องตัดหญ้าเบนซิน GX-35 4 จังหวะสำหรับใช้ในครัวเรือน เครื่องตัดหญ้าไร้สายขนาดเล็กเครื่องตัดหญ้าน้ำมันเบนซิน</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</v>
       </c>
       <c r="D5" t="str">
-        <v>1499.00</v>
+        <v>2680.00</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G5" t="str">
-        <v>ขายได้ 39 ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>https://shopee.co.th/product/0/27467423728</v>
+        <v>https://shopee.co.th/product/0/43259115829</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/7pqV5S2fho</v>
+        <v>https://s.shopee.co.th/W44PaeA44</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>ป้ายฟิวเจอร์บอร์ดคนละครึ่งพลัสขนาด A4 A3ป้ายร้านค้าไทยช่วยไทย</v>
+        <v>CIVAGOxLucky Puppy （26oz/780ml） แก้วกาแฟสแตนเลสซับเซรามิกพร้อมฝาปิดกระติกน้ําสูญญากาศแก้วน้ําร้อนและเย็น</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mo3jx74mfdhc39.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-ml67nm0lt2q764.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>69.00</v>
+        <v>470.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>53</v>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 613 ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/45110217360</v>
+        <v>https://shopee.co.th/product/0/57956483494</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/9zuzfR3dRa</v>
+        <v>https://s.shopee.co.th/2qRzBsepmP</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -632,37 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>น้ำยาขจัดคราบน้ำกระจกและหินปูนในห้องน้ำ MARS</v>
+        <v>Mobi GARDEN เก้าอี้ปิกนิก พับได้ แบบพกพา สวยหรู สําหรับตั้งแคมป์กลางแจ้ง</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m659yr5og8bu23.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7qukw-lh7ao27q1gpr5c.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>249.00</v>
+        <v>926.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 4พัน+ ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/13125750201</v>
+        <v>https://shopee.co.th/product/0/23069023714</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/4AxCiiY1UB</v>
+        <v>https://s.shopee.co.th/9Uyt88J1tR</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -670,31 +670,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>【ส่งถึงในวันเดียวกัน】เครื่องตัดหญ้าไฟฟ้า ไร้สาย แบต2ก้อน 50000mah ง่ายต่อการพกพา พับเก็บได้ Lawn mower</v>
+        <v>เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ แบบพกพา พร้อมปั๊มลมในตัว ที่นอนลม แบบหนา 40/25ซม</v>
       </c>
       <c r="C8" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0i-mbxoukw7r6mr1c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m66kvsnez2tt31.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>729.00</v>
+        <v>1039.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G8" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 10พัน+ ชิ้น</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>https://shopee.co.th/product/0/41705956403</v>
+        <v>https://shopee.co.th/product/0/25326987298</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/BR3xMw3AR</v>
+        <v>https://s.shopee.co.th/6fehkvh5FI</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -708,37 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>หมอน ErgoLab Deep Sleep หมดปัญหาปวดคอ ไม่ต้องกังวลเรื่องกรน หลับสบายต่อเนื่องตลอดคืน (คืนเงินใน 90 วัน + รับประกัน 1 ปี)</v>
+        <v>ลวดหนาม (ชุบกัลวาไนซ์) ยาว120-200m (เบอร์14 16 17) ล้อมรั้วราคาถูก ลวดหนามเหล็กติดรั้ว ล้อมรั้ว ลวดหนาม</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lop0pq60fv3x2c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>1690.00</v>
+        <v>675.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 90พัน+ ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/23922419352</v>
+        <v>https://shopee.co.th/product/0/5379453788</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/9ALsfuYa4e</v>
+        <v>https://s.shopee.co.th/1LdBP86PE9</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -746,37 +746,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>TYESO รุ่นใหม่ 2026 แก้วเก็บความเย็นลายดอกไม้ 900ML แก้วเก็บอุณหภูมิสแตนเลส พร้อมหลอด เก็บเย็น 24H ร้อน 12H</v>
+        <v>TYESO TS-8829 TS-8830 แก้วน้ําสุญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด 1050 มล. 1200 มล.</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m8n1ynp79ckycb.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>319.00</v>
+        <v>419.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 419 ชิ้น</v>
+        <v>ขายได้ 8พัน+ ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/54857018813</v>
+        <v>https://shopee.co.th/product/0/20385393992</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/7VDegqiufO</v>
+        <v>https://s.shopee.co.th/7AayLqsNaB</v>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>12.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -784,31 +784,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Sipeau 10 แพ็ค กระดาษทิชชู่ กระดาษชําระ หนาเป็นพิเศษ ทนน้ำ ใช้ได้ทั้งแบบดึงด้านล่าง เหมาะสำหรับใช้ได้ทุกที่</v>
+        <v>YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ดูดยุงร้ายให้ตายในทันที แบบ 360 องศา ปกป้องคนที่คุณรัก โคมดักยุง</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm1kxjjdv7db2b.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/9db66f2b508e0216fbd10afbdedebe8c.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>179.00</v>
+        <v>497.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G11" t="str">
-        <v>ขายได้ 460 ชิ้น</v>
+        <v>ขายได้ 60พัน+ ชิ้น</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/56557684434</v>
+        <v>https://shopee.co.th/product/0/4749406757</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/50WJiG0KuX</v>
+        <v>https://s.shopee.co.th/5L9KAU8uki</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -822,19 +822,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Makita เครื่องตัดหญ้าไร้สายแบบ 388Vf เครื่องเล็มหญ้าแบบดูอัลแอคชั่น เครื่องตัดหญ้าในสวน</v>
+        <v>TTRacing Duo V4 Chopper One Piece Edition Gaming Chair เก้าอี้สำนักงาน เก้าอี้เกมมิ่ง - รับประกัน 2 ปี</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rash-maximzfnvalwf1.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3thzgdxy4g51.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>1575.00</v>
+        <v>4821.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G12" t="str">
         <v>ขายได้ 1พัน+ ชิ้น</v>
@@ -843,16 +843,16 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/19284718210</v>
+        <v>https://shopee.co.th/product/0/24723053806</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/W3uLzQXdl</v>
+        <v>https://s.shopee.co.th/6py7xFBexZ</v>
       </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -860,37 +860,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>ZINSANO เครื่องฉีดน้ำแรงดันสูง 80-120 บาร์ รุ่น AMAZON ULTRA/ZN1101/FA0803/FA1005 ล้างรถ ดูดฝุ่น ฉีดพื้น รับประกัน 1 ปี</v>
+        <v>ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ปริมาณ 180ML</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lpov09alxgxcec.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-ml3hnx0lnuo587.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>4620.00</v>
+        <v>204.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>90</v>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 20พัน+ ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/25653050667</v>
+        <v>https://shopee.co.th/product/0/7348642178</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/6VL7V1BXMH</v>
+        <v>https://s.shopee.co.th/6VLHYdN6Re</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -898,37 +898,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>ส่งจากไทย🚚Miffy แก้วกาแฟ มัทฉะ ถ้วยมัทฉะ แก้วน้ำ แก้วการ์ตูน ตกแต่งคาเฟ่ ถ้วยเซรามิก ริเริ่มความคิด</v>
+        <v>TYESO 01-01022/23/24/25/26 600ML/750MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญากาศพร้อมฝาปิด 2-in-1 และฟาง,ถ้วยกาแฟสแตนเลสผนังคู่แก้วเดินทางป้องกันการรั่วพลิก</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mk0m1nqpb6rl65.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-mcd890h82m5o60.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>337.00</v>
+        <v>339.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 112 ชิ้น</v>
+        <v>ขายได้ 20พัน+ ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/44027481267</v>
+        <v>https://shopee.co.th/product/0/43304958355</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/5fm0VUNZsO</v>
+        <v>https://s.shopee.co.th/1BJlCpoQ0x</v>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         <v>55</v>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 5พัน+ ชิ้น</v>
+        <v>ขายได้ 6พัน+ ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -960,7 +960,7 @@
         <v>https://shopee.co.th/product/0/45957704286</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/2VoyjfiZOM</v>
+        <v>https://s.shopee.co.th/8ATVXhS24W</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -974,37 +974,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Maybuck เครื่องตัดหญ้าเบนซิน GX-35 4 จังหวะสำหรับใช้ในครัวเรือน เครื่องตัดหญ้าไร้สายขนาดเล็กเครื่องตัดหญ้าน้ำมันเบนซิน</v>
+        <v>TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้าเดียว(คิตตี้,คุโรมิ,ชินนาม่อนโรล,มายเมโลดี้)ประกัน 1ปี</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mozceyjaky69f5.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>2560.00</v>
+        <v>3851.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 4พัน+ ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/43259115829</v>
+        <v>https://shopee.co.th/product/0/16761796915</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/4ftTJegRLc</v>
+        <v>https://s.shopee.co.th/4VaDAxu5GU</v>
       </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1012,13 +1012,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>ZINSANO เครื่องฉีดน้ำแรงดันสูง AD Series 110,140,160,180 บาร์ | Induction motor ทนทาน งานมืออาชีพ</v>
+        <v>ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ไม่ต้องเจาะ ที่วางของในห้องน้ำ ชั้นใส่ของ</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0k-md1hurbdvs918c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkjqydbkcq9x48.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>9790.00</v>
+        <v>169.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1027,22 +1027,22 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 172 ชิ้น</v>
+        <v>ขายได้ 151 ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/42661578906</v>
+        <v>https://shopee.co.th/product/0/51106057326</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/9KfIsEam13</v>
+        <v>https://s.shopee.co.th/80A5LOksuD</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1050,37 +1050,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>🐕พร้อมส่ง🐶 น้องดัชชุนสุดฮิต DACHSHUND //เขียนการ์ดฟรี 🥺🤎</v>
+        <v>TYESO TS-8826 TS-8827 TS-8828 600 มล. 750 มล. 900 มล. แก้วน้ําสูญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/d79d4536e03944c292cfcc00a004b9e9.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mel4uxcc4hz7fd.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>889.00</v>
+        <v>329.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G18" t="str">
-        <v>ขายได้ 382 ชิ้น</v>
+        <v>ขายได้ 10พัน+ ชิ้น</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/12929257757</v>
+        <v>https://shopee.co.th/product/0/20285394571</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/6L1hIirLlu</v>
+        <v>https://s.shopee.co.th/1gG1nlJ22I</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1088,37 +1088,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>ถังน้ําแข็ง ถังสแตนเลส ถังพักชา ถังน้ําแข็ง6/8/10/12ลิตร ถังชาเก็บความเย็น/ร้อนเก็บชานม ไขมุกน้ำผลไม</v>
+        <v>มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ ถูบ้าน ปลอดภัยกับเด็ก และ สัตว์เลี้ยง มิลินคลีน</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgn3lu1sly4o99.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>389.00</v>
+        <v>294.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G19" t="str">
-        <v>ขายได้ 105 ชิ้น</v>
+        <v>ขายได้ 10พัน+ ชิ้น</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/44800790903</v>
+        <v>https://shopee.co.th/product/0/29805541583</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/2g8OvzDDMr</v>
+        <v>https://s.shopee.co.th/3LOFmpJlfB</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -1126,31 +1126,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>เครื่องตัดหญ้าสะพายบ่า NIPPON NP35 | NP50MAX2.5HP/ NP35MAX1.8HPครบชุด แถมใบตัด4แบบ ✔ ประกัน1ปี</v>
+        <v>เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ถึง160°c สีครีม เบาะฟองน้ำหนา10ซม. นุ่มสบาย ผ้ากำมะหยี่</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mop8p3guoi686f.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>1896.00</v>
+        <v>1499.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>62</v>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 4พัน+ ชิ้น</v>
+        <v>ขายได้ 43 ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/28429411253</v>
+        <v>https://shopee.co.th/product/0/27467423728</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/3VhVvWJjeP</v>
+        <v>https://s.shopee.co.th/9pbjWm5Xax</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1164,37 +1164,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>TYESO 01-01022/23/24/25/26 600ML/750MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญากาศพร้อมฝาปิด 2-in-1 และฟาง,ถ้วยกาแฟสแตนเลสผนังคู่แก้วเดินทางป้องกันการรั่วพลิก</v>
+        <v>ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ปริมาณ 180ML</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-mcd890h82m5o60.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-ml3hoam25nggae.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>349.00</v>
+        <v>223.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 7พัน+ ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/43304958355</v>
+        <v>https://shopee.co.th/product/0/28223885891</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/AUrGGO0Vle</v>
+        <v>https://s.shopee.co.th/9pbjWmDzqV</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
